--- a/Tables/COMBAT_RULE_DATA.xlsx
+++ b/Tables/COMBAT_RULE_DATA.xlsx
@@ -1183,12 +1183,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletSizeMultTbd</t>
+          <t xml:space="preserve">tagBeamCellsTbd</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1.5</t>
         </is>
       </c>
       <c r="F45">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletWavesTbd</t>
+          <t xml:space="preserve">tagBeamSecondsTbd</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">0.3</t>
         </is>
       </c>
       <c r="F46">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletWaveSecondsTbd</t>
+          <t xml:space="preserve">tagWaveCountTbd</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.22</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F47">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">invincibleBlinkSecondsTbd</t>
+          <t xml:space="preserve">tagWaveIntervalSecondsTbd</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.06</t>
+          <t xml:space="preserve">0.15</t>
         </is>
       </c>
       <c r="F48">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">invincibleBlinkMinAlphaTbd</t>
+          <t xml:space="preserve">tagWaveSecondsTbd</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3</t>
+          <t xml:space="preserve">0.45</t>
         </is>
       </c>
       <c r="F49">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemyProjectileViewUnitsTbd</t>
+          <t xml:space="preserve">tagBulletSizeMultTbd</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F50">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
+          <t xml:space="preserve">태그 스킬 연출 (260908_W04 2-3 · 사용자 확정)</t>
         </is>
       </c>
       <c r="C51">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">droneAoeRingOn</t>
+          <t xml:space="preserve">tagBulletWavesTbd</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F51">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
+          <t xml:space="preserve">태그 스킬 연출 (260908_W04 2-3 · 사용자 확정)</t>
         </is>
       </c>
       <c r="C52">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideStepHoldTbd</t>
+          <t xml:space="preserve">tagBulletWaveSecondsTbd</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.4</t>
+          <t xml:space="preserve">0.22</t>
         </is>
       </c>
       <c r="F52">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
+          <t xml:space="preserve">태그 스킬 연출 (260908_W04 2-3 · 사용자 확정)</t>
         </is>
       </c>
       <c r="C53">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideDetourCellsTbd</t>
+          <t xml:space="preserve">invincibleBlinkSecondsTbd</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">0.06</t>
         </is>
       </c>
       <c r="F53">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">피격 VFX 셋 (2026-09-16 설치)</t>
+          <t xml:space="preserve">태그 스킬 연출 (260908_W04 2-3 · 사용자 확정)</t>
         </is>
       </c>
       <c r="C54">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ammoOutScaleAssumed</t>
+          <t xml:space="preserve">invincibleBlinkMinAlphaTbd</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.5</t>
+          <t xml:space="preserve">0.3</t>
         </is>
       </c>
       <c r="F54">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">태그 스킬 연출 (260908_W04 2-3 · 사용자 확정)</t>
         </is>
       </c>
       <c r="C55">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">vfxOneShotSeconds</t>
+          <t xml:space="preserve">enemyProjectileViewUnitsTbd</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.2</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F55">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
         </is>
       </c>
       <c r="C56">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">waveSizeTbd</t>
+          <t xml:space="preserve">droneAoeRingOn</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F56">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
         </is>
       </c>
       <c r="C57">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">waveIntervalSecondsTbd</t>
+          <t xml:space="preserve">enemySideStepHoldTbd</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">0.4</t>
         </is>
       </c>
       <c r="F57">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
         </is>
       </c>
       <c r="C58">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropRestSecondsTbd</t>
+          <t xml:space="preserve">enemySideDetourCellsTbd</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.25</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F58">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
         </is>
       </c>
       <c r="C59">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropMagnetSecondsTbd</t>
+          <t xml:space="preserve">enemySideDetourRecoverSecondsTbd</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.45</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F59">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
         </is>
       </c>
       <c r="C60">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropViewUnitsTbd</t>
+          <t xml:space="preserve">enemyPushStrengthTbd</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F60">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">피격 VFX 셋 (2026-09-16 설치)</t>
         </is>
       </c>
       <c r="C61">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropPopSecondsTbd</t>
+          <t xml:space="preserve">ammoOutScaleAssumed</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.9</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F61">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropPopRiseUnitsTbd</t>
+          <t xml:space="preserve">vfxOneShotSeconds</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8</t>
+          <t xml:space="preserve">0.2</t>
         </is>
       </c>
       <c r="F62">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">combatPowerMountFactorTbd</t>
+          <t xml:space="preserve">waveSizeTbd</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F63">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeAfterimageCountTbd</t>
+          <t xml:space="preserve">waveIntervalSecondsTbd</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F64">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeTrailSecondsTbd</t>
+          <t xml:space="preserve">dropRestSecondsTbd</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.6</t>
+          <t xml:space="preserve">0.25</t>
         </is>
       </c>
       <c r="F65">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeAfterimageAlphaTbd</t>
+          <t xml:space="preserve">dropMagnetSecondsTbd</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeStreakThicknessTbd</t>
+          <t xml:space="preserve">dropViewUnitsTbd</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.35</t>
+          <t xml:space="preserve">0.3</t>
         </is>
       </c>
       <c r="F67">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">shotsPerRound</t>
+          <t xml:space="preserve">dropPopSecondsTbd</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">0.9</t>
         </is>
       </c>
       <c r="F68">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">shotDamageFactor</t>
+          <t xml:space="preserve">dropPopRiseUnitsTbd</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.5</t>
+          <t xml:space="preserve">0.8</t>
         </is>
       </c>
       <c r="F69">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
         </is>
       </c>
       <c r="C70">
@@ -1833,12 +1833,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiShotCountTbd</t>
+          <t xml:space="preserve">dropPopSideUnitsTbd</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1.1</t>
         </is>
       </c>
       <c r="F70">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
         </is>
       </c>
       <c r="C71">
@@ -1859,12 +1859,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">aoeRadiusTbd</t>
+          <t xml:space="preserve">combatPowerMountFactorTbd</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F71">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
         </is>
       </c>
       <c r="C72">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">aoeSplashFactorTbd</t>
+          <t xml:space="preserve">dodgeAfterimageCountTbd</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F72">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">수동 회피 입력 — 화면 플릭</t>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
         </is>
       </c>
       <c r="C73">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">flickMinPixelsTbd</t>
+          <t xml:space="preserve">dodgeTrailSecondsTbd</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">0.6</t>
         </is>
       </c>
       <c r="F73">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">수동 회피 입력 — 화면 플릭</t>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
         </is>
       </c>
       <c r="C74">
@@ -1937,15 +1937,223 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">dodgeAfterimageAlphaTbd</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.45</t>
+        </is>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>73</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dodgeStreakThicknessTbd</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.35</t>
+        </is>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>74</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shotsPerRound</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>75</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shotDamageFactor</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.5</t>
+        </is>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>76</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">multiShotCountTbd</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>77</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aoeRadiusTbd</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>78</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aoeSplashFactorTbd</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수동 회피 입력 — 화면 플릭</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>79</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flickMinPixelsTbd</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40</t>
+        </is>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수동 회피 입력 — 화면 플릭</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>80</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
           <t xml:space="preserve">flickMaxSecondsTbd</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t xml:space="preserve">0.3</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="F82">
         <v>0</v>
       </c>
     </row>
@@ -3126,12 +3334,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletSizeMultTbd</t>
+          <t xml:space="preserve">tagBeamCellsTbd</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1.5</t>
         </is>
       </c>
       <c r="F45">
@@ -3152,12 +3360,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletWavesTbd</t>
+          <t xml:space="preserve">tagBeamSecondsTbd</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">0.3</t>
         </is>
       </c>
       <c r="F46">
@@ -3178,12 +3386,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletWaveSecondsTbd</t>
+          <t xml:space="preserve">tagWaveCountTbd</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.22</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F47">
@@ -3204,12 +3412,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">invincibleBlinkSecondsTbd</t>
+          <t xml:space="preserve">tagWaveIntervalSecondsTbd</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.06</t>
+          <t xml:space="preserve">0.15</t>
         </is>
       </c>
       <c r="F48">
@@ -3230,12 +3438,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">invincibleBlinkMinAlphaTbd</t>
+          <t xml:space="preserve">tagWaveSecondsTbd</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3</t>
+          <t xml:space="preserve">0.45</t>
         </is>
       </c>
       <c r="F49">
@@ -3256,12 +3464,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemyProjectileViewUnitsTbd</t>
+          <t xml:space="preserve">tagBulletSizeMultTbd</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F50">
@@ -3274,7 +3482,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
+          <t xml:space="preserve">태그 스킬 연출 (260908_W04 2-3 · 사용자 확정)</t>
         </is>
       </c>
       <c r="C51">
@@ -3282,12 +3490,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">droneAoeRingOn</t>
+          <t xml:space="preserve">tagBulletWavesTbd</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F51">
@@ -3300,7 +3508,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
+          <t xml:space="preserve">태그 스킬 연출 (260908_W04 2-3 · 사용자 확정)</t>
         </is>
       </c>
       <c r="C52">
@@ -3308,12 +3516,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideStepHoldTbd</t>
+          <t xml:space="preserve">tagBulletWaveSecondsTbd</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.4</t>
+          <t xml:space="preserve">0.22</t>
         </is>
       </c>
       <c r="F52">
@@ -3326,7 +3534,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
+          <t xml:space="preserve">태그 스킬 연출 (260908_W04 2-3 · 사용자 확정)</t>
         </is>
       </c>
       <c r="C53">
@@ -3334,12 +3542,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideDetourCellsTbd</t>
+          <t xml:space="preserve">invincibleBlinkSecondsTbd</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">0.06</t>
         </is>
       </c>
       <c r="F53">
@@ -3352,7 +3560,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">피격 VFX 셋 (2026-09-16 설치)</t>
+          <t xml:space="preserve">태그 스킬 연출 (260908_W04 2-3 · 사용자 확정)</t>
         </is>
       </c>
       <c r="C54">
@@ -3360,12 +3568,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ammoOutScaleAssumed</t>
+          <t xml:space="preserve">invincibleBlinkMinAlphaTbd</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.5</t>
+          <t xml:space="preserve">0.3</t>
         </is>
       </c>
       <c r="F54">
@@ -3378,7 +3586,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">태그 스킬 연출 (260908_W04 2-3 · 사용자 확정)</t>
         </is>
       </c>
       <c r="C55">
@@ -3386,12 +3594,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">vfxOneShotSeconds</t>
+          <t xml:space="preserve">enemyProjectileViewUnitsTbd</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.2</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F55">
@@ -3404,7 +3612,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
         </is>
       </c>
       <c r="C56">
@@ -3412,12 +3620,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">waveSizeTbd</t>
+          <t xml:space="preserve">droneAoeRingOn</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F56">
@@ -3430,7 +3638,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
         </is>
       </c>
       <c r="C57">
@@ -3438,12 +3646,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">waveIntervalSecondsTbd</t>
+          <t xml:space="preserve">enemySideStepHoldTbd</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">0.4</t>
         </is>
       </c>
       <c r="F57">
@@ -3456,7 +3664,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
         </is>
       </c>
       <c r="C58">
@@ -3464,12 +3672,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropRestSecondsTbd</t>
+          <t xml:space="preserve">enemySideDetourCellsTbd</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.25</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F58">
@@ -3482,7 +3690,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
         </is>
       </c>
       <c r="C59">
@@ -3490,12 +3698,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropMagnetSecondsTbd</t>
+          <t xml:space="preserve">enemySideDetourRecoverSecondsTbd</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.45</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F59">
@@ -3508,7 +3716,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
         </is>
       </c>
       <c r="C60">
@@ -3516,12 +3724,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropViewUnitsTbd</t>
+          <t xml:space="preserve">enemyPushStrengthTbd</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F60">
@@ -3534,7 +3742,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">피격 VFX 셋 (2026-09-16 설치)</t>
         </is>
       </c>
       <c r="C61">
@@ -3542,12 +3750,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropPopSecondsTbd</t>
+          <t xml:space="preserve">ammoOutScaleAssumed</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.9</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F61">
@@ -3568,12 +3776,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropPopRiseUnitsTbd</t>
+          <t xml:space="preserve">vfxOneShotSeconds</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8</t>
+          <t xml:space="preserve">0.2</t>
         </is>
       </c>
       <c r="F62">
@@ -3594,12 +3802,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">combatPowerMountFactorTbd</t>
+          <t xml:space="preserve">waveSizeTbd</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F63">
@@ -3620,12 +3828,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeAfterimageCountTbd</t>
+          <t xml:space="preserve">waveIntervalSecondsTbd</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F64">
@@ -3646,12 +3854,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeTrailSecondsTbd</t>
+          <t xml:space="preserve">dropRestSecondsTbd</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.6</t>
+          <t xml:space="preserve">0.25</t>
         </is>
       </c>
       <c r="F65">
@@ -3672,7 +3880,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeAfterimageAlphaTbd</t>
+          <t xml:space="preserve">dropMagnetSecondsTbd</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3698,12 +3906,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeStreakThicknessTbd</t>
+          <t xml:space="preserve">dropViewUnitsTbd</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.35</t>
+          <t xml:space="preserve">0.3</t>
         </is>
       </c>
       <c r="F67">
@@ -3724,12 +3932,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">shotsPerRound</t>
+          <t xml:space="preserve">dropPopSecondsTbd</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">0.9</t>
         </is>
       </c>
       <c r="F68">
@@ -3750,12 +3958,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">shotDamageFactor</t>
+          <t xml:space="preserve">dropPopRiseUnitsTbd</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.5</t>
+          <t xml:space="preserve">0.8</t>
         </is>
       </c>
       <c r="F69">
@@ -3768,7 +3976,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
         </is>
       </c>
       <c r="C70">
@@ -3776,12 +3984,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiShotCountTbd</t>
+          <t xml:space="preserve">dropPopSideUnitsTbd</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1.1</t>
         </is>
       </c>
       <c r="F70">
@@ -3794,7 +4002,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
         </is>
       </c>
       <c r="C71">
@@ -3802,12 +4010,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">aoeRadiusTbd</t>
+          <t xml:space="preserve">combatPowerMountFactorTbd</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F71">
@@ -3820,7 +4028,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
         </is>
       </c>
       <c r="C72">
@@ -3828,12 +4036,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">aoeSplashFactorTbd</t>
+          <t xml:space="preserve">dodgeAfterimageCountTbd</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F72">
@@ -3846,7 +4054,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">수동 회피 입력 — 화면 플릭</t>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
         </is>
       </c>
       <c r="C73">
@@ -3854,12 +4062,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">flickMinPixelsTbd</t>
+          <t xml:space="preserve">dodgeTrailSecondsTbd</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">0.6</t>
         </is>
       </c>
       <c r="F73">
@@ -3872,7 +4080,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">수동 회피 입력 — 화면 플릭</t>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
         </is>
       </c>
       <c r="C74">
@@ -3880,15 +4088,223 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">dodgeAfterimageAlphaTbd</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.45</t>
+        </is>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>73</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dodgeStreakThicknessTbd</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.35</t>
+        </is>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>74</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shotsPerRound</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>75</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shotDamageFactor</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.5</t>
+        </is>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>76</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">multiShotCountTbd</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>77</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aoeRadiusTbd</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>78</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aoeSplashFactorTbd</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수동 회피 입력 — 화면 플릭</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>79</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flickMinPixelsTbd</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40</t>
+        </is>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수동 회피 입력 — 화면 플릭</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>80</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
           <t xml:space="preserve">flickMaxSecondsTbd</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t xml:space="preserve">0.3</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="F82">
         <v>0</v>
       </c>
     </row>
@@ -5165,7 +5581,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 구현 가정 — 태그 섬광이 가장 밝을 때의 알파. 1 이면 화면이 통째로 가려진다.</t>
+          <t xml:space="preserve">🗑️ 폐기(2026-09-21) — 구 태그 섬광 알파. 읽는 곳 없음.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5190,7 +5606,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 구현 가정 — 태그 섬광이 스치는 시간(초). 짧을수록 덜 가린다.</t>
+          <t xml:space="preserve">🗑️ 폐기(2026-09-21) — 구 태그 섬광 시간. 읽는 곳 없음.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5210,12 +5626,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletSizeMultTbd</t>
+          <t xml:space="preserve">tagBeamCellsTbd</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 구현 가정 — 탄환 크기 배율. 1 이면 자산 제 크기(아트 픽셀 기준).</t>
+          <t xml:space="preserve">⚠️ 가정 — 빔 굵기(칸). 「굵게」만 받았다.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5235,12 +5651,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletWavesTbd</t>
+          <t xml:space="preserve">tagBeamSecondsTbd</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 구현 가정 — 탄환비가 내려오는 파도 수. 3~4 사이를 사용자가 청했다.</t>
+          <t xml:space="preserve">⚠️ 가정 — 빔이 머무는 시간(초).</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5260,12 +5676,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletWaveSecondsTbd</t>
+          <t xml:space="preserve">tagWaveCountTbd</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 구현 가정 — 파도 하나가 내려오는 시간(초). 작을수록 빠르게 떨어진다.</t>
+          <t xml:space="preserve">⚠️ 가정 — 파동을 몇 번 내보내는가. 사용자 말은 「2~3번」이었다.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5285,12 +5701,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">invincibleBlinkSecondsTbd</t>
+          <t xml:space="preserve">tagWaveIntervalSecondsTbd</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">🗑️ 폐기(2026-09-18 저녁) — 무적 깜빡임을 걷었다. 읽는 곳이 없다.</t>
+          <t xml:space="preserve">⚠️ 가정 — 파동 사이 간격(초).</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5310,12 +5726,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">invincibleBlinkMinAlphaTbd</t>
+          <t xml:space="preserve">tagWaveSecondsTbd</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">🗑️ 폐기(2026-09-18 저녁) — 무적 깜빡임을 걷었다. 읽는 곳이 없다.</t>
+          <t xml:space="preserve">⚠️ 가정 — 파동 하나가 반경 0 에서 화면 끝까지 커지는 데 걸리는 시간(초).</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5335,12 +5751,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemyProjectileViewUnitsTbd</t>
+          <t xml:space="preserve">tagBulletSizeMultTbd</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 구현 가정 — 적 포탄 한 변(월드 유닛). 격자 한 칸 = 1. 구 0.25(09-18 전).</t>
+          <t xml:space="preserve">⚠️ 구현 가정 — 탄환 크기 배율. 1 이면 자산 제 크기(아트 픽셀 기준).</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5360,12 +5776,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">droneAoeRingOn</t>
+          <t xml:space="preserve">tagBulletWavesTbd</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">광역형 범위 고리를 그릴지(자리표시든 아트든). 2026-09-18 부터 켜짐 — 판정 반경 2칸을 그린다.</t>
+          <t xml:space="preserve">⚠️ 구현 가정 — 탄환비가 내려오는 파도 수. 3~4 사이를 사용자가 청했다.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5385,12 +5801,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideStepHoldTbd</t>
+          <t xml:space="preserve">tagBulletWaveSecondsTbd</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">적이 부 축으로 곁눈질한 방향을 붙드는 시간(초). ⚠️ 가정 — 매 틱 다시 고르면 두 축이 비슷할 때 좌우가 뒤집혀 제자리에서 떠는 것처럼 보인다. 0 이면 안 붙든다.</t>
+          <t xml:space="preserve">⚠️ 구현 가정 — 파도 하나가 내려오는 시간(초). 작을수록 빠르게 떨어진다.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5410,12 +5826,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideDetourCellsTbd</t>
+          <t xml:space="preserve">invincibleBlinkSecondsTbd</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">적이 곁눈질로 돌아갈 수 있는 최대 거리(칸). ✅ 사용자 확정 3 (2026-09-19) — 「어려워짐을 감수하고 켠다」. 켠 판이 출하 판이다. 0 이면 종전 거동(표적까지 남은 양까지만 · 굳음 100% 길막). 크면 적이 표적을 두고 옆으로 오래 미끄러진다. ⚠️ 몇 칸이 옳은지는 여전히 설계 몫이다 — 3 은 처음 재 본 값이다.</t>
+          <t xml:space="preserve">🗑️ 폐기(2026-09-18 저녁) — 무적 깜빡임을 걷었다. 읽는 곳이 없다.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5435,12 +5851,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">ammoOutScaleAssumed</t>
+          <t xml:space="preserve">invincibleBlinkMinAlphaTbd</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">탄약 소진 아이콘을 몇 배로 줄여 그리는가. ⚠️ 가정 — 연출 문서에 크기 절이 없다. 0.5 는 아이콘 실루엣(212px)이 로봇 실루엣(220px)의 절반 이하가 되는 값이며 상한은 EffectTiming.AmmoOutScaleMax(0.52). 설계가 연출 문서에 역기입할 자리다.</t>
+          <t xml:space="preserve">🗑️ 폐기(2026-09-18 저녁) — 무적 깜빡임을 걷었다. 읽는 곳이 없다.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5460,12 +5876,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">vfxOneShotSeconds</t>
+          <t xml:space="preserve">enemyProjectileViewUnitsTbd</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">위 셋이 한 번 그려지고 사라지는 데 걸리는 초. 이펙트는 로봇보다 짧게 끝난다(연출 2장).</t>
+          <t xml:space="preserve">⚠️ 구현 가정 — 적 포탄 한 변(월드 유닛). 격자 한 칸 = 1. 구 0.25(09-18 전).</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5485,12 +5901,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">waveSizeTbd</t>
+          <t xml:space="preserve">droneAoeRingOn</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 한 묶음에 나오는 적 수. 1 이면 종전(한 마리씩) 모델과 같다.</t>
+          <t xml:space="preserve">광역형 범위 고리를 그릴지(자리표시든 아트든). 2026-09-18 부터 켜짐 — 판정 반경 2칸을 그린다.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5510,12 +5926,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">waveIntervalSecondsTbd</t>
+          <t xml:space="preserve">enemySideStepHoldTbd</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 묶음 간격(초). 0 이면 waveSizeTbd × spawnCadenceTbd 로 끌어온다(평균 불변).</t>
+          <t xml:space="preserve">적이 부 축으로 곁눈질한 방향을 붙드는 시간(초). ⚠️ 가정 — 매 틱 다시 고르면 두 축이 비슷할 때 좌우가 뒤집혀 제자리에서 떠는 것처럼 보인다. 0 이면 안 붙든다.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5535,12 +5951,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropRestSecondsTbd</t>
+          <t xml:space="preserve">enemySideDetourCellsTbd</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 떨어져 멈춰 있는 시간(초). 이 동안은 안 빨린다.</t>
+          <t xml:space="preserve">적이 곁눈질로 돌아갈 수 있는 최대 거리(칸). ✅ 사용자 확정 3 (2026-09-19) — 「어려워짐을 감수하고 켠다」. 켠 판이 출하 판이다. 0 이면 종전 거동(표적까지 남은 양까지만 · 굳음 100% 길막). 크면 적이 표적을 두고 옆으로 오래 미끄러진다. ⚠️ 몇 칸이 옳은지는 여전히 설계 몫이다 — 3 은 처음 재 본 값이다.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5560,12 +5976,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropMagnetSecondsTbd</t>
+          <t xml:space="preserve">enemySideDetourRecoverSecondsTbd</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 로봇에게 빨려 들어가는 데 걸리는 시간(초).</t>
+          <t xml:space="preserve">⚠️ 가정 — 다 쓴 곁눈질 예산이 가득 차는 데 걸리는 시간(초). 0 이면 안 돌아온다(구 거동 · 굳는다).</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5585,12 +6001,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropViewUnitsTbd</t>
+          <t xml:space="preserve">enemyPushStrengthTbd</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 떨어진 재화의 화면 크기(유닛).</t>
+          <t xml:space="preserve">⚠️ 가정 — 겹친 적끼리 서로 미는 세기(초당 배). 0 이면 안 민다(구 거동 · 2026-09-16 규칙).</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5610,12 +6026,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropPopSecondsTbd</t>
+          <t xml:space="preserve">ammoOutScaleAssumed</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 「+12 스크랩」 글자가 떠 있는 시간(초).</t>
+          <t xml:space="preserve">탄약 소진 아이콘을 몇 배로 줄여 그리는가. ⚠️ 가정 — 연출 문서에 크기 절이 없다. 0.5 는 아이콘 실루엣(212px)이 로봇 실루엣(220px)의 절반 이하가 되는 값이며 상한은 EffectTiming.AmmoOutScaleMax(0.52). 설계가 연출 문서에 역기입할 자리다.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5635,12 +6051,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropPopRiseUnitsTbd</t>
+          <t xml:space="preserve">vfxOneShotSeconds</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 팝 글자가 떠오르는 높이(유닛).</t>
+          <t xml:space="preserve">위 셋이 한 번 그려지고 사라지는 데 걸리는 초. 이펙트는 로봇보다 짧게 끝난다(연출 2장).</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5660,12 +6076,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">combatPowerMountFactorTbd</t>
+          <t xml:space="preserve">waveSizeTbd</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 미확정(설계 판정 대기) — 0 이면 전투력 = 물류 출력 그대로. &gt;0 이면 (1 + 적재율 × 이 값) 을 곱한다.</t>
+          <t xml:space="preserve">⚠️ 가정 — 한 묶음에 나오는 적 수. 1 이면 종전(한 마리씩) 모델과 같다.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5685,12 +6101,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeAfterimageCountTbd</t>
+          <t xml:space="preserve">waveIntervalSecondsTbd</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 회피 잔상 장수. 사용자 육안으로 3 에서 5 로(09-18). 0 이면 규칙 기본값 3.</t>
+          <t xml:space="preserve">⚠️ 가정 — 묶음 간격(초). 0 이면 waveSizeTbd × spawnCadenceTbd 로 끌어온다(평균 불변).</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5710,12 +6126,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeTrailSecondsTbd</t>
+          <t xml:space="preserve">dropRestSecondsTbd</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 잔상·줄기가 사라지는 시간(초). 사용자 육안 50% 증가 — 0.4 에서 0.6(09-18).</t>
+          <t xml:space="preserve">⚠️ 가정 — 떨어져 멈춰 있는 시간(초). 이 동안은 안 빨린다.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5735,12 +6151,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeAfterimageAlphaTbd</t>
+          <t xml:space="preserve">dropMagnetSecondsTbd</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 가장 진한 잔상의 옅기(0~1). 1 이면 로봇이 여럿으로 보인다.</t>
+          <t xml:space="preserve">⚠️ 가정 — 로봇에게 빨려 들어가는 데 걸리는 시간(초).</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5760,12 +6176,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeStreakThicknessTbd</t>
+          <t xml:space="preserve">dropViewUnitsTbd</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 줄기 두께(유닛). 길이는 회피 거리가 정한다.</t>
+          <t xml:space="preserve">⚠️ 가정 — 떨어진 재화의 화면 크기(유닛).</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5785,12 +6201,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">shotsPerRound</t>
+          <t xml:space="preserve">dropPopSecondsTbd</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용자 확정 — 탄약 한 발을 소비할 때 나가는 발 수(3). 1 이면 구 거동.</t>
+          <t xml:space="preserve">⚠️ 가정 — 「+12 스크랩」 글자가 떠 있는 시간(초).</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5810,12 +6226,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">shotDamageFactor</t>
+          <t xml:space="preserve">dropPopRiseUnitsTbd</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용자 확정 — 한 발의 피해 배수(0.5). 1 이면 구 거동.</t>
+          <t xml:space="preserve">⚠️ 가정 — 팝 글자가 떠오르는 높이(유닛).</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5835,12 +6251,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiShotCountTbd</t>
+          <t xml:space="preserve">dropPopSideUnitsTbd</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">멀티샷 표적 수. 로봇A 표준탄 = 1(단일). 다중은 드론 역할.</t>
+          <t xml:space="preserve">⚠️ 가정 — 흡수 글자가 로봇 중심에서 옆으로 떨어진 거리(유닛). 로봇 그림 위에 겹치지 않을 만큼.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5860,12 +6276,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">aoeRadiusTbd</t>
+          <t xml:space="preserve">combatPowerMountFactorTbd</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">AoE 스플래시 반경(유닛). 로봇A 폭발탄은 splashFactor 0이라 무효(드론용 보존).</t>
+          <t xml:space="preserve">⚠️ 미확정(설계 판정 대기) — 0 이면 전투력 = 물류 출력 그대로. &gt;0 이면 (1 + 적재율 × 이 값) 을 곱한다.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5885,12 +6301,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">aoeSplashFactorTbd</t>
+          <t xml:space="preserve">dodgeAfterimageCountTbd</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">AoE 스플래시 배율. 로봇A 폭발탄 = 0(스플래시 없음, 단일 표적). 드론 광역형이 &gt;0 사용.</t>
+          <t xml:space="preserve">⚠️ 가정 — 회피 잔상 장수. 사용자 육안으로 3 에서 5 로(09-18). 0 이면 규칙 기본값 3.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5910,12 +6326,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">flickMinPixelsTbd</t>
+          <t xml:space="preserve">dodgeTrailSecondsTbd</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD — 플릭으로 인정할 최소 이동(픽셀). chat+Notion 확정 필요.</t>
+          <t xml:space="preserve">⚠️ 가정 — 잔상·줄기가 사라지는 시간(초). 사용자 육안 50% 증가 — 0.4 에서 0.6(09-18).</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5935,20 +6351,220 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t xml:space="preserve">dodgeAfterimageAlphaTbd</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠️ 가정 — 가장 진한 잔상의 옅기(0~1). 1 이면 로봇이 여럿으로 보인다.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C# [Tooltip] 에서 그대로</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data\CombatTuning.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>79</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dodgeStreakThicknessTbd</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠️ 가정 — 줄기 두께(유닛). 길이는 회피 거리가 정한다.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C# [Tooltip] 에서 그대로</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data\CombatTuning.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>80</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shotsPerRound</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용자 확정 — 탄약 한 발을 소비할 때 나가는 발 수(3). 1 이면 구 거동.</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C# [Tooltip] 에서 그대로</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data\CombatTuning.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>81</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shotDamageFactor</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용자 확정 — 한 발의 피해 배수(0.5). 1 이면 구 거동.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C# [Tooltip] 에서 그대로</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data\CombatTuning.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>82</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">multiShotCountTbd</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">멀티샷 표적 수. 로봇A 표준탄 = 1(단일). 다중은 드론 역할.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C# [Tooltip] 에서 그대로</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data\CombatTuning.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>83</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aoeRadiusTbd</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AoE 스플래시 반경(유닛). 로봇A 폭발탄은 splashFactor 0이라 무효(드론용 보존).</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C# [Tooltip] 에서 그대로</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data\CombatTuning.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>84</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aoeSplashFactorTbd</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AoE 스플래시 배율. 로봇A 폭발탄 = 0(스플래시 없음, 단일 표적). 드론 광역형이 &gt;0 사용.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C# [Tooltip] 에서 그대로</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data\CombatTuning.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>85</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flickMinPixelsTbd</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD — 플릭으로 인정할 최소 이동(픽셀). chat+Notion 확정 필요.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C# [Tooltip] 에서 그대로</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data\CombatTuning.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>86</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t xml:space="preserve">flickMaxSecondsTbd</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t xml:space="preserve">TBD — 플릭으로 인정할 최대 시간(초). 이보다 오래 끌면 드래그로 본다.</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C# [Tooltip] 에서 그대로</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C# [Tooltip] 에서 그대로</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">Data\CombatTuning.cs</t>
         </is>

--- a/Tables/COMBAT_RULE_DATA.xlsx
+++ b/Tables/COMBAT_RULE_DATA.xlsx
@@ -1209,12 +1209,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBeamSecondsTbd</t>
+          <t xml:space="preserve">droneBeamCellsTbd</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3</t>
+          <t xml:space="preserve">0.12</t>
         </is>
       </c>
       <c r="F46">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagWaveCountTbd</t>
+          <t xml:space="preserve">tagBeamSecondsTbd</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">0.3</t>
         </is>
       </c>
       <c r="F47">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagWaveIntervalSecondsTbd</t>
+          <t xml:space="preserve">tagWaveCountTbd</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.15</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F48">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagWaveSecondsTbd</t>
+          <t xml:space="preserve">tagWaveIntervalSecondsTbd</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.45</t>
+          <t xml:space="preserve">0.15</t>
         </is>
       </c>
       <c r="F49">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletSizeMultTbd</t>
+          <t xml:space="preserve">tagWaveSecondsTbd</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">0.45</t>
         </is>
       </c>
       <c r="F50">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletWavesTbd</t>
+          <t xml:space="preserve">tagBulletSizeMultTbd</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F51">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletWaveSecondsTbd</t>
+          <t xml:space="preserve">tagBulletWavesTbd</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.22</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F52">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">invincibleBlinkSecondsTbd</t>
+          <t xml:space="preserve">tagBulletWaveSecondsTbd</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.06</t>
+          <t xml:space="preserve">0.22</t>
         </is>
       </c>
       <c r="F53">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">invincibleBlinkMinAlphaTbd</t>
+          <t xml:space="preserve">invincibleBlinkSecondsTbd</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3</t>
+          <t xml:space="preserve">0.06</t>
         </is>
       </c>
       <c r="F54">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemyProjectileViewUnitsTbd</t>
+          <t xml:space="preserve">invincibleBlinkMinAlphaTbd</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.5</t>
+          <t xml:space="preserve">0.3</t>
         </is>
       </c>
       <c r="F55">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
+          <t xml:space="preserve">태그 스킬 연출 (260908_W04 2-3 · 사용자 확정)</t>
         </is>
       </c>
       <c r="C56">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">droneAoeRingOn</t>
+          <t xml:space="preserve">enemyProjectileViewUnitsTbd</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F56">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideStepHoldTbd</t>
+          <t xml:space="preserve">droneAoeRingOn</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F57">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideDetourCellsTbd</t>
+          <t xml:space="preserve">enemySideStepHoldTbd</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">0.4</t>
         </is>
       </c>
       <c r="F58">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideDetourRecoverSecondsTbd</t>
+          <t xml:space="preserve">enemySideDetourCellsTbd</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F59">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemyPushStrengthTbd</t>
+          <t xml:space="preserve">enemySideDetourRecoverSecondsTbd</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F60">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">피격 VFX 셋 (2026-09-16 설치)</t>
+          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
         </is>
       </c>
       <c r="C61">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">ammoOutScaleAssumed</t>
+          <t xml:space="preserve">enemyPushStrengthTbd</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F61">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">피격 VFX 셋 (2026-09-16 설치)</t>
         </is>
       </c>
       <c r="C62">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">vfxOneShotSeconds</t>
+          <t xml:space="preserve">ammoOutScaleAssumed</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.2</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F62">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">waveSizeTbd</t>
+          <t xml:space="preserve">vfxOneShotSeconds</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">0.2</t>
         </is>
       </c>
       <c r="F63">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">waveIntervalSecondsTbd</t>
+          <t xml:space="preserve">waveSizeTbd</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F64">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropRestSecondsTbd</t>
+          <t xml:space="preserve">waveIntervalSecondsTbd</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.25</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F65">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropMagnetSecondsTbd</t>
+          <t xml:space="preserve">dropRestSecondsTbd</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.45</t>
+          <t xml:space="preserve">0.25</t>
         </is>
       </c>
       <c r="F66">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropViewUnitsTbd</t>
+          <t xml:space="preserve">dropMagnetSecondsTbd</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3</t>
+          <t xml:space="preserve">0.45</t>
         </is>
       </c>
       <c r="F67">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropPopSecondsTbd</t>
+          <t xml:space="preserve">dropViewUnitsTbd</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.9</t>
+          <t xml:space="preserve">0.3</t>
         </is>
       </c>
       <c r="F68">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropPopRiseUnitsTbd</t>
+          <t xml:space="preserve">dropPopSecondsTbd</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8</t>
+          <t xml:space="preserve">0.9</t>
         </is>
       </c>
       <c r="F69">
@@ -1833,12 +1833,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropPopSideUnitsTbd</t>
+          <t xml:space="preserve">dropPopRiseUnitsTbd</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.1</t>
+          <t xml:space="preserve">0.8</t>
         </is>
       </c>
       <c r="F70">
@@ -1859,12 +1859,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">combatPowerMountFactorTbd</t>
+          <t xml:space="preserve">dropPopSideUnitsTbd</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1.1</t>
         </is>
       </c>
       <c r="F71">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeAfterimageCountTbd</t>
+          <t xml:space="preserve">combatPowerMountFactorTbd</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F72">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeTrailSecondsTbd</t>
+          <t xml:space="preserve">dodgeAfterimageCountTbd</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F73">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeAfterimageAlphaTbd</t>
+          <t xml:space="preserve">dodgeTrailSecondsTbd</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.45</t>
+          <t xml:space="preserve">0.6</t>
         </is>
       </c>
       <c r="F74">
@@ -1963,12 +1963,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeStreakThicknessTbd</t>
+          <t xml:space="preserve">dodgeAfterimageAlphaTbd</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.35</t>
+          <t xml:space="preserve">0.45</t>
         </is>
       </c>
       <c r="F75">
@@ -1989,12 +1989,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">shotsPerRound</t>
+          <t xml:space="preserve">dodgeStreakThicknessTbd</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">0.35</t>
         </is>
       </c>
       <c r="F76">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">shotDamageFactor</t>
+          <t xml:space="preserve">shotsPerRound</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F77">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
         </is>
       </c>
       <c r="C78">
@@ -2041,12 +2041,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiShotCountTbd</t>
+          <t xml:space="preserve">shotDamageFactor</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F78">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">aoeRadiusTbd</t>
+          <t xml:space="preserve">multiShotCountTbd</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F79">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">aoeSplashFactorTbd</t>
+          <t xml:space="preserve">aoeRadiusTbd</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1.5</t>
         </is>
       </c>
       <c r="F80">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">수동 회피 입력 — 화면 플릭</t>
+          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
         </is>
       </c>
       <c r="C81">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">flickMinPixelsTbd</t>
+          <t xml:space="preserve">aoeSplashFactorTbd</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F81">
@@ -2145,15 +2145,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">flickMinPixelsTbd</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40</t>
+        </is>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수동 회피 입력 — 화면 플릭</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>81</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
           <t xml:space="preserve">flickMaxSecondsTbd</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t xml:space="preserve">0.3</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="F83">
         <v>0</v>
       </c>
     </row>
@@ -3360,12 +3386,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBeamSecondsTbd</t>
+          <t xml:space="preserve">droneBeamCellsTbd</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3</t>
+          <t xml:space="preserve">0.12</t>
         </is>
       </c>
       <c r="F46">
@@ -3386,12 +3412,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagWaveCountTbd</t>
+          <t xml:space="preserve">tagBeamSecondsTbd</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">0.3</t>
         </is>
       </c>
       <c r="F47">
@@ -3412,12 +3438,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagWaveIntervalSecondsTbd</t>
+          <t xml:space="preserve">tagWaveCountTbd</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.15</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F48">
@@ -3438,12 +3464,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagWaveSecondsTbd</t>
+          <t xml:space="preserve">tagWaveIntervalSecondsTbd</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.45</t>
+          <t xml:space="preserve">0.15</t>
         </is>
       </c>
       <c r="F49">
@@ -3464,12 +3490,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletSizeMultTbd</t>
+          <t xml:space="preserve">tagWaveSecondsTbd</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">0.45</t>
         </is>
       </c>
       <c r="F50">
@@ -3490,12 +3516,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletWavesTbd</t>
+          <t xml:space="preserve">tagBulletSizeMultTbd</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F51">
@@ -3516,12 +3542,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletWaveSecondsTbd</t>
+          <t xml:space="preserve">tagBulletWavesTbd</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.22</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F52">
@@ -3542,12 +3568,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">invincibleBlinkSecondsTbd</t>
+          <t xml:space="preserve">tagBulletWaveSecondsTbd</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.06</t>
+          <t xml:space="preserve">0.22</t>
         </is>
       </c>
       <c r="F53">
@@ -3568,12 +3594,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">invincibleBlinkMinAlphaTbd</t>
+          <t xml:space="preserve">invincibleBlinkSecondsTbd</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3</t>
+          <t xml:space="preserve">0.06</t>
         </is>
       </c>
       <c r="F54">
@@ -3594,12 +3620,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemyProjectileViewUnitsTbd</t>
+          <t xml:space="preserve">invincibleBlinkMinAlphaTbd</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.5</t>
+          <t xml:space="preserve">0.3</t>
         </is>
       </c>
       <c r="F55">
@@ -3612,7 +3638,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
+          <t xml:space="preserve">태그 스킬 연출 (260908_W04 2-3 · 사용자 확정)</t>
         </is>
       </c>
       <c r="C56">
@@ -3620,12 +3646,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">droneAoeRingOn</t>
+          <t xml:space="preserve">enemyProjectileViewUnitsTbd</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F56">
@@ -3646,12 +3672,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideStepHoldTbd</t>
+          <t xml:space="preserve">droneAoeRingOn</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F57">
@@ -3672,12 +3698,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideDetourCellsTbd</t>
+          <t xml:space="preserve">enemySideStepHoldTbd</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">0.4</t>
         </is>
       </c>
       <c r="F58">
@@ -3698,12 +3724,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideDetourRecoverSecondsTbd</t>
+          <t xml:space="preserve">enemySideDetourCellsTbd</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F59">
@@ -3724,12 +3750,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemyPushStrengthTbd</t>
+          <t xml:space="preserve">enemySideDetourRecoverSecondsTbd</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F60">
@@ -3742,7 +3768,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">피격 VFX 셋 (2026-09-16 설치)</t>
+          <t xml:space="preserve">설치된 VFX 자산 (2026-09-08 배선 · 260908_W06 6장)</t>
         </is>
       </c>
       <c r="C61">
@@ -3750,12 +3776,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">ammoOutScaleAssumed</t>
+          <t xml:space="preserve">enemyPushStrengthTbd</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F61">
@@ -3768,7 +3794,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
+          <t xml:space="preserve">피격 VFX 셋 (2026-09-16 설치)</t>
         </is>
       </c>
       <c r="C62">
@@ -3776,12 +3802,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">vfxOneShotSeconds</t>
+          <t xml:space="preserve">ammoOutScaleAssumed</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.2</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F62">
@@ -3802,12 +3828,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">waveSizeTbd</t>
+          <t xml:space="preserve">vfxOneShotSeconds</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">0.2</t>
         </is>
       </c>
       <c r="F63">
@@ -3828,12 +3854,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">waveIntervalSecondsTbd</t>
+          <t xml:space="preserve">waveSizeTbd</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F64">
@@ -3854,12 +3880,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropRestSecondsTbd</t>
+          <t xml:space="preserve">waveIntervalSecondsTbd</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.25</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F65">
@@ -3880,12 +3906,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropMagnetSecondsTbd</t>
+          <t xml:space="preserve">dropRestSecondsTbd</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.45</t>
+          <t xml:space="preserve">0.25</t>
         </is>
       </c>
       <c r="F66">
@@ -3906,12 +3932,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropViewUnitsTbd</t>
+          <t xml:space="preserve">dropMagnetSecondsTbd</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3</t>
+          <t xml:space="preserve">0.45</t>
         </is>
       </c>
       <c r="F67">
@@ -3932,12 +3958,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropPopSecondsTbd</t>
+          <t xml:space="preserve">dropViewUnitsTbd</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.9</t>
+          <t xml:space="preserve">0.3</t>
         </is>
       </c>
       <c r="F68">
@@ -3958,12 +3984,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropPopRiseUnitsTbd</t>
+          <t xml:space="preserve">dropPopSecondsTbd</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8</t>
+          <t xml:space="preserve">0.9</t>
         </is>
       </c>
       <c r="F69">
@@ -3984,12 +4010,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropPopSideUnitsTbd</t>
+          <t xml:space="preserve">dropPopRiseUnitsTbd</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.1</t>
+          <t xml:space="preserve">0.8</t>
         </is>
       </c>
       <c r="F70">
@@ -4010,12 +4036,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">combatPowerMountFactorTbd</t>
+          <t xml:space="preserve">dropPopSideUnitsTbd</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1.1</t>
         </is>
       </c>
       <c r="F71">
@@ -4036,12 +4062,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeAfterimageCountTbd</t>
+          <t xml:space="preserve">combatPowerMountFactorTbd</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F72">
@@ -4062,12 +4088,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeTrailSecondsTbd</t>
+          <t xml:space="preserve">dodgeAfterimageCountTbd</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F73">
@@ -4088,12 +4114,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeAfterimageAlphaTbd</t>
+          <t xml:space="preserve">dodgeTrailSecondsTbd</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.45</t>
+          <t xml:space="preserve">0.6</t>
         </is>
       </c>
       <c r="F74">
@@ -4114,12 +4140,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeStreakThicknessTbd</t>
+          <t xml:space="preserve">dodgeAfterimageAlphaTbd</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.35</t>
+          <t xml:space="preserve">0.45</t>
         </is>
       </c>
       <c r="F75">
@@ -4140,12 +4166,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">shotsPerRound</t>
+          <t xml:space="preserve">dodgeStreakThicknessTbd</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">0.35</t>
         </is>
       </c>
       <c r="F76">
@@ -4166,12 +4192,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">shotDamageFactor</t>
+          <t xml:space="preserve">shotsPerRound</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F77">
@@ -4184,7 +4210,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
+          <t xml:space="preserve">전투 배경 (2026-09-09 배선)</t>
         </is>
       </c>
       <c r="C78">
@@ -4192,12 +4218,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiShotCountTbd</t>
+          <t xml:space="preserve">shotDamageFactor</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F78">
@@ -4218,12 +4244,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">aoeRadiusTbd</t>
+          <t xml:space="preserve">multiShotCountTbd</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F79">
@@ -4244,12 +4270,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">aoeSplashFactorTbd</t>
+          <t xml:space="preserve">aoeRadiusTbd</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1.5</t>
         </is>
       </c>
       <c r="F80">
@@ -4262,7 +4288,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">수동 회피 입력 — 화면 플릭</t>
+          <t xml:space="preserve">히트 패턴 (로봇A 탄종 = 단일 표적)</t>
         </is>
       </c>
       <c r="C81">
@@ -4270,12 +4296,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">flickMinPixelsTbd</t>
+          <t xml:space="preserve">aoeSplashFactorTbd</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F81">
@@ -4296,15 +4322,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">flickMinPixelsTbd</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40</t>
+        </is>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수동 회피 입력 — 화면 플릭</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>81</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
           <t xml:space="preserve">flickMaxSecondsTbd</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t xml:space="preserve">0.3</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="F83">
         <v>0</v>
       </c>
     </row>
@@ -5651,12 +5703,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBeamSecondsTbd</t>
+          <t xml:space="preserve">droneBeamCellsTbd</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 빔이 머무는 시간(초).</t>
+          <t xml:space="preserve">⚠️ 가정 — 누적형 드론이 붙은 적에게 쏘는 조사 빔의 굵기(칸). 태그 빔보다 훨씬 가늘다.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5676,12 +5728,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagWaveCountTbd</t>
+          <t xml:space="preserve">tagBeamSecondsTbd</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 파동을 몇 번 내보내는가. 사용자 말은 「2~3번」이었다.</t>
+          <t xml:space="preserve">⚠️ 가정 — 빔이 머무는 시간(초).</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5701,12 +5753,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagWaveIntervalSecondsTbd</t>
+          <t xml:space="preserve">tagWaveCountTbd</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 파동 사이 간격(초).</t>
+          <t xml:space="preserve">⚠️ 가정 — 파동을 몇 번 내보내는가. 사용자 말은 「2~3번」이었다.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5726,12 +5778,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagWaveSecondsTbd</t>
+          <t xml:space="preserve">tagWaveIntervalSecondsTbd</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 파동 하나가 반경 0 에서 화면 끝까지 커지는 데 걸리는 시간(초).</t>
+          <t xml:space="preserve">⚠️ 가정 — 파동 사이 간격(초).</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5751,12 +5803,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletSizeMultTbd</t>
+          <t xml:space="preserve">tagWaveSecondsTbd</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 구현 가정 — 탄환 크기 배율. 1 이면 자산 제 크기(아트 픽셀 기준).</t>
+          <t xml:space="preserve">⚠️ 가정 — 파동 하나가 반경 0 에서 화면 끝까지 커지는 데 걸리는 시간(초).</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5776,12 +5828,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletWavesTbd</t>
+          <t xml:space="preserve">tagBulletSizeMultTbd</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 구현 가정 — 탄환비가 내려오는 파도 수. 3~4 사이를 사용자가 청했다.</t>
+          <t xml:space="preserve">⚠️ 구현 가정 — 탄환 크기 배율. 1 이면 자산 제 크기(아트 픽셀 기준).</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5801,12 +5853,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagBulletWaveSecondsTbd</t>
+          <t xml:space="preserve">tagBulletWavesTbd</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 구현 가정 — 파도 하나가 내려오는 시간(초). 작을수록 빠르게 떨어진다.</t>
+          <t xml:space="preserve">⚠️ 구현 가정 — 탄환비가 내려오는 파도 수. 3~4 사이를 사용자가 청했다.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5826,12 +5878,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">invincibleBlinkSecondsTbd</t>
+          <t xml:space="preserve">tagBulletWaveSecondsTbd</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">🗑️ 폐기(2026-09-18 저녁) — 무적 깜빡임을 걷었다. 읽는 곳이 없다.</t>
+          <t xml:space="preserve">⚠️ 구현 가정 — 파도 하나가 내려오는 시간(초). 작을수록 빠르게 떨어진다.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5851,7 +5903,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">invincibleBlinkMinAlphaTbd</t>
+          <t xml:space="preserve">invincibleBlinkSecondsTbd</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5876,12 +5928,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemyProjectileViewUnitsTbd</t>
+          <t xml:space="preserve">invincibleBlinkMinAlphaTbd</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 구현 가정 — 적 포탄 한 변(월드 유닛). 격자 한 칸 = 1. 구 0.25(09-18 전).</t>
+          <t xml:space="preserve">🗑️ 폐기(2026-09-18 저녁) — 무적 깜빡임을 걷었다. 읽는 곳이 없다.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5901,12 +5953,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">droneAoeRingOn</t>
+          <t xml:space="preserve">enemyProjectileViewUnitsTbd</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">광역형 범위 고리를 그릴지(자리표시든 아트든). 2026-09-18 부터 켜짐 — 판정 반경 2칸을 그린다.</t>
+          <t xml:space="preserve">⚠️ 구현 가정 — 적 포탄 한 변(월드 유닛). 격자 한 칸 = 1. 구 0.25(09-18 전).</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5926,12 +5978,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideStepHoldTbd</t>
+          <t xml:space="preserve">droneAoeRingOn</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">적이 부 축으로 곁눈질한 방향을 붙드는 시간(초). ⚠️ 가정 — 매 틱 다시 고르면 두 축이 비슷할 때 좌우가 뒤집혀 제자리에서 떠는 것처럼 보인다. 0 이면 안 붙든다.</t>
+          <t xml:space="preserve">광역형 범위 고리를 그릴지(자리표시든 아트든). 2026-09-18 부터 켜짐 — 판정 반경 2칸을 그린다.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5951,12 +6003,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideDetourCellsTbd</t>
+          <t xml:space="preserve">enemySideStepHoldTbd</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">적이 곁눈질로 돌아갈 수 있는 최대 거리(칸). ✅ 사용자 확정 3 (2026-09-19) — 「어려워짐을 감수하고 켠다」. 켠 판이 출하 판이다. 0 이면 종전 거동(표적까지 남은 양까지만 · 굳음 100% 길막). 크면 적이 표적을 두고 옆으로 오래 미끄러진다. ⚠️ 몇 칸이 옳은지는 여전히 설계 몫이다 — 3 은 처음 재 본 값이다.</t>
+          <t xml:space="preserve">적이 부 축으로 곁눈질한 방향을 붙드는 시간(초). ⚠️ 가정 — 매 틱 다시 고르면 두 축이 비슷할 때 좌우가 뒤집혀 제자리에서 떠는 것처럼 보인다. 0 이면 안 붙든다.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5976,12 +6028,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideDetourRecoverSecondsTbd</t>
+          <t xml:space="preserve">enemySideDetourCellsTbd</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 다 쓴 곁눈질 예산이 가득 차는 데 걸리는 시간(초). 0 이면 안 돌아온다(구 거동 · 굳는다).</t>
+          <t xml:space="preserve">적이 곁눈질로 돌아갈 수 있는 최대 거리(칸). ✅ 사용자 확정 3 (2026-09-19) — 「어려워짐을 감수하고 켠다」. 켠 판이 출하 판이다. 0 이면 종전 거동(표적까지 남은 양까지만 · 굳음 100% 길막). 크면 적이 표적을 두고 옆으로 오래 미끄러진다. ⚠️ 몇 칸이 옳은지는 여전히 설계 몫이다 — 3 은 처음 재 본 값이다.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6001,12 +6053,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemyPushStrengthTbd</t>
+          <t xml:space="preserve">enemySideDetourRecoverSecondsTbd</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 겹친 적끼리 서로 미는 세기(초당 배). 0 이면 안 민다(구 거동 · 2026-09-16 규칙).</t>
+          <t xml:space="preserve">⚠️ 가정 — 다 쓴 곁눈질 예산이 가득 차는 데 걸리는 시간(초). 0 이면 안 돌아온다(구 거동 · 굳는다).</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6026,12 +6078,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ammoOutScaleAssumed</t>
+          <t xml:space="preserve">enemyPushStrengthTbd</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">탄약 소진 아이콘을 몇 배로 줄여 그리는가. ⚠️ 가정 — 연출 문서에 크기 절이 없다. 0.5 는 아이콘 실루엣(212px)이 로봇 실루엣(220px)의 절반 이하가 되는 값이며 상한은 EffectTiming.AmmoOutScaleMax(0.52). 설계가 연출 문서에 역기입할 자리다.</t>
+          <t xml:space="preserve">⚠️ 가정 — 겹친 적끼리 서로 미는 세기(초당 배). 0 이면 안 민다(구 거동 · 2026-09-16 규칙).</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6051,12 +6103,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">vfxOneShotSeconds</t>
+          <t xml:space="preserve">ammoOutScaleAssumed</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">위 셋이 한 번 그려지고 사라지는 데 걸리는 초. 이펙트는 로봇보다 짧게 끝난다(연출 2장).</t>
+          <t xml:space="preserve">탄약 소진 아이콘을 몇 배로 줄여 그리는가. ⚠️ 가정 — 연출 문서에 크기 절이 없다. 0.5 는 아이콘 실루엣(212px)이 로봇 실루엣(220px)의 절반 이하가 되는 값이며 상한은 EffectTiming.AmmoOutScaleMax(0.52). 설계가 연출 문서에 역기입할 자리다.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6076,12 +6128,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">waveSizeTbd</t>
+          <t xml:space="preserve">vfxOneShotSeconds</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 한 묶음에 나오는 적 수. 1 이면 종전(한 마리씩) 모델과 같다.</t>
+          <t xml:space="preserve">위 셋이 한 번 그려지고 사라지는 데 걸리는 초. 이펙트는 로봇보다 짧게 끝난다(연출 2장).</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6101,12 +6153,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">waveIntervalSecondsTbd</t>
+          <t xml:space="preserve">waveSizeTbd</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 묶음 간격(초). 0 이면 waveSizeTbd × spawnCadenceTbd 로 끌어온다(평균 불변).</t>
+          <t xml:space="preserve">⚠️ 가정 — 한 묶음에 나오는 적 수. 1 이면 종전(한 마리씩) 모델과 같다.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6126,12 +6178,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropRestSecondsTbd</t>
+          <t xml:space="preserve">waveIntervalSecondsTbd</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 떨어져 멈춰 있는 시간(초). 이 동안은 안 빨린다.</t>
+          <t xml:space="preserve">⚠️ 가정 — 묶음 간격(초). 0 이면 waveSizeTbd × spawnCadenceTbd 로 끌어온다(평균 불변).</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6151,12 +6203,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropMagnetSecondsTbd</t>
+          <t xml:space="preserve">dropRestSecondsTbd</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 로봇에게 빨려 들어가는 데 걸리는 시간(초).</t>
+          <t xml:space="preserve">⚠️ 가정 — 떨어져 멈춰 있는 시간(초). 이 동안은 안 빨린다.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6176,12 +6228,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropViewUnitsTbd</t>
+          <t xml:space="preserve">dropMagnetSecondsTbd</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 떨어진 재화의 화면 크기(유닛).</t>
+          <t xml:space="preserve">⚠️ 가정 — 로봇에게 빨려 들어가는 데 걸리는 시간(초).</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6201,12 +6253,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropPopSecondsTbd</t>
+          <t xml:space="preserve">dropViewUnitsTbd</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 「+12 스크랩」 글자가 떠 있는 시간(초).</t>
+          <t xml:space="preserve">⚠️ 가정 — 떨어진 재화의 화면 크기(유닛).</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6226,12 +6278,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropPopRiseUnitsTbd</t>
+          <t xml:space="preserve">dropPopSecondsTbd</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 팝 글자가 떠오르는 높이(유닛).</t>
+          <t xml:space="preserve">⚠️ 가정 — 「+12 스크랩」 글자가 떠 있는 시간(초).</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6251,12 +6303,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">dropPopSideUnitsTbd</t>
+          <t xml:space="preserve">dropPopRiseUnitsTbd</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 흡수 글자가 로봇 중심에서 옆으로 떨어진 거리(유닛). 로봇 그림 위에 겹치지 않을 만큼.</t>
+          <t xml:space="preserve">⚠️ 가정 — 팝 글자가 떠오르는 높이(유닛).</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6276,12 +6328,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">combatPowerMountFactorTbd</t>
+          <t xml:space="preserve">dropPopSideUnitsTbd</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 미확정(설계 판정 대기) — 0 이면 전투력 = 물류 출력 그대로. &gt;0 이면 (1 + 적재율 × 이 값) 을 곱한다.</t>
+          <t xml:space="preserve">⚠️ 가정 — 흡수 글자가 로봇 중심에서 옆으로 떨어진 거리(유닛). 로봇 그림 위에 겹치지 않을 만큼.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6301,12 +6353,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeAfterimageCountTbd</t>
+          <t xml:space="preserve">combatPowerMountFactorTbd</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 회피 잔상 장수. 사용자 육안으로 3 에서 5 로(09-18). 0 이면 규칙 기본값 3.</t>
+          <t xml:space="preserve">⚠️ 미확정(설계 판정 대기) — 0 이면 전투력 = 물류 출력 그대로. &gt;0 이면 (1 + 적재율 × 이 값) 을 곱한다.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6326,12 +6378,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeTrailSecondsTbd</t>
+          <t xml:space="preserve">dodgeAfterimageCountTbd</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 잔상·줄기가 사라지는 시간(초). 사용자 육안 50% 증가 — 0.4 에서 0.6(09-18).</t>
+          <t xml:space="preserve">⚠️ 가정 — 회피 잔상 장수. 사용자 육안으로 3 에서 5 로(09-18). 0 이면 규칙 기본값 3.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6351,12 +6403,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeAfterimageAlphaTbd</t>
+          <t xml:space="preserve">dodgeTrailSecondsTbd</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 가장 진한 잔상의 옅기(0~1). 1 이면 로봇이 여럿으로 보인다.</t>
+          <t xml:space="preserve">⚠️ 가정 — 잔상·줄기가 사라지는 시간(초). 사용자 육안 50% 증가 — 0.4 에서 0.6(09-18).</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6376,12 +6428,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeStreakThicknessTbd</t>
+          <t xml:space="preserve">dodgeAfterimageAlphaTbd</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 줄기 두께(유닛). 길이는 회피 거리가 정한다.</t>
+          <t xml:space="preserve">⚠️ 가정 — 가장 진한 잔상의 옅기(0~1). 1 이면 로봇이 여럿으로 보인다.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6401,12 +6453,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">shotsPerRound</t>
+          <t xml:space="preserve">dodgeStreakThicknessTbd</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용자 확정 — 탄약 한 발을 소비할 때 나가는 발 수(3). 1 이면 구 거동.</t>
+          <t xml:space="preserve">⚠️ 가정 — 줄기 두께(유닛). 길이는 회피 거리가 정한다.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6426,12 +6478,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">shotDamageFactor</t>
+          <t xml:space="preserve">shotsPerRound</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용자 확정 — 한 발의 피해 배수(0.5). 1 이면 구 거동.</t>
+          <t xml:space="preserve">사용자 확정 — 탄약 한 발을 소비할 때 나가는 발 수(3). 1 이면 구 거동.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6451,12 +6503,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiShotCountTbd</t>
+          <t xml:space="preserve">shotDamageFactor</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">멀티샷 표적 수. 로봇A 표준탄 = 1(단일). 다중은 드론 역할.</t>
+          <t xml:space="preserve">사용자 확정 — 한 발의 피해 배수(0.5). 1 이면 구 거동.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6476,12 +6528,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">aoeRadiusTbd</t>
+          <t xml:space="preserve">multiShotCountTbd</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">AoE 스플래시 반경(유닛). 로봇A 폭발탄은 splashFactor 0이라 무효(드론용 보존).</t>
+          <t xml:space="preserve">멀티샷 표적 수. 로봇A 표준탄 = 1(단일). 다중은 드론 역할.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6501,12 +6553,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">aoeSplashFactorTbd</t>
+          <t xml:space="preserve">aoeRadiusTbd</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">AoE 스플래시 배율. 로봇A 폭발탄 = 0(스플래시 없음, 단일 표적). 드론 광역형이 &gt;0 사용.</t>
+          <t xml:space="preserve">AoE 스플래시 반경(유닛). 로봇A 폭발탄은 splashFactor 0이라 무효(드론용 보존).</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6526,12 +6578,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">flickMinPixelsTbd</t>
+          <t xml:space="preserve">aoeSplashFactorTbd</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD — 플릭으로 인정할 최소 이동(픽셀). chat+Notion 확정 필요.</t>
+          <t xml:space="preserve">AoE 스플래시 배율. 로봇A 폭발탄 = 0(스플래시 없음, 단일 표적). 드론 광역형이 &gt;0 사용.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6551,20 +6603,45 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t xml:space="preserve">flickMinPixelsTbd</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD — 플릭으로 인정할 최소 이동(픽셀). chat+Notion 확정 필요.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C# [Tooltip] 에서 그대로</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data\CombatTuning.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>87</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t xml:space="preserve">flickMaxSecondsTbd</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t xml:space="preserve">TBD — 플릭으로 인정할 최대 시간(초). 이보다 오래 끌면 드래그로 본다.</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C# [Tooltip] 에서 그대로</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C# [Tooltip] 에서 그대로</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">Data\CombatTuning.cs</t>
         </is>

--- a/Tables/COMBAT_RULE_DATA.xlsx
+++ b/Tables/COMBAT_RULE_DATA.xlsx
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F45">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3</t>
+          <t xml:space="preserve">0.15</t>
         </is>
       </c>
       <c r="F47">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideDetourRecoverSecondsTbd</t>
+          <t xml:space="preserve">enemyPushStrengthTbd</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F60">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemyPushStrengthTbd</t>
+          <t xml:space="preserve">enemySideDetourRecoverSecondsTbd</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F61">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5</t>
+          <t xml:space="preserve">0.5</t>
         </is>
       </c>
       <c r="F45">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3</t>
+          <t xml:space="preserve">0.15</t>
         </is>
       </c>
       <c r="F47">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideDetourRecoverSecondsTbd</t>
+          <t xml:space="preserve">enemyPushStrengthTbd</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F60">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemyPushStrengthTbd</t>
+          <t xml:space="preserve">enemySideDetourRecoverSecondsTbd</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F61">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 빔 굵기(칸). 「굵게」만 받았다.</t>
+          <t xml:space="preserve">⚠️ 가정 — 빔 굵기(칸). 판이 아니라 줄기로 읽히게 가늘다.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 빔이 머무는 시간(초).</t>
+          <t xml:space="preserve">⚠️ 가정 — 빔이 머무는 시간(초). 짧을수록 덜 덮는다.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemySideDetourRecoverSecondsTbd</t>
+          <t xml:space="preserve">enemyPushStrengthTbd</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 다 쓴 곁눈질 예산이 가득 차는 데 걸리는 시간(초). 0 이면 안 돌아온다(구 거동 · 굳는다).</t>
+          <t xml:space="preserve">⚠️ 가정 — 겹친 적끼리 서로 미는 세기(초당 배). 0 이면 안 민다(구 거동 · 2026-09-16 규칙).</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6078,12 +6078,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">enemyPushStrengthTbd</t>
+          <t xml:space="preserve">enemySideDetourRecoverSecondsTbd</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 가정 — 겹친 적끼리 서로 미는 세기(초당 배). 0 이면 안 민다(구 거동 · 2026-09-16 규칙).</t>
+          <t xml:space="preserve">⚠️ 가정 — 다 쓴 곁눈질 예산이 가득 차는 데 걸리는 시간(초). 0 이면 안 돌아온다(구 거동 · 굳는다).</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">

--- a/Tables/COMBAT_RULE_DATA.xlsx
+++ b/Tables/COMBAT_RULE_DATA.xlsx
@@ -174,7 +174,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F6">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F6">
@@ -4706,11 +4706,6 @@
           <t xml:space="preserve">autoPilotHoldWhenMoreThanTbd</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD — 사거리 안 적이 이 수를 넘으면 제자리 사격. 이하면 가장 가까운 무리로 이동.</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t xml:space="preserve">C# [Tooltip] 에서 그대로</t>
